--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/45.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/45.xlsx
@@ -426,13 +426,13 @@
         <v>-12.63782297724743</v>
       </c>
       <c r="E2">
-        <v>-29.40031350313403</v>
+        <v>-35.36682707431015</v>
       </c>
       <c r="F2">
-        <v>-4.165856702885193</v>
+        <v>-5.63749800404223</v>
       </c>
       <c r="G2">
-        <v>-19.77956062124391</v>
+        <v>-25.94570163432471</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.25282318945351</v>
       </c>
       <c r="E3">
-        <v>-30.77242754203613</v>
+        <v>-34.40566299465613</v>
       </c>
       <c r="F3">
-        <v>-3.892478179614993</v>
+        <v>-5.602117222038355</v>
       </c>
       <c r="G3">
-        <v>-20.65716306988592</v>
+        <v>-26.03979892546018</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.86615062277787</v>
       </c>
       <c r="E4">
-        <v>-31.6227458991674</v>
+        <v>-36.81256730786595</v>
       </c>
       <c r="F4">
-        <v>-4.108093405178412</v>
+        <v>-6.049289256910006</v>
       </c>
       <c r="G4">
-        <v>-20.28486573963056</v>
+        <v>-25.79277760422915</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.4972380388912</v>
       </c>
       <c r="E5">
-        <v>-30.58154330566481</v>
+        <v>-35.50411002808968</v>
       </c>
       <c r="F5">
-        <v>-4.192651423268513</v>
+        <v>-5.761381023718608</v>
       </c>
       <c r="G5">
-        <v>-20.10937206532103</v>
+        <v>-24.45447467252385</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.11926303255579</v>
       </c>
       <c r="E6">
-        <v>-30.61812658293577</v>
+        <v>-37.82960596406362</v>
       </c>
       <c r="F6">
-        <v>-3.591086274259543</v>
+        <v>-5.438583749210077</v>
       </c>
       <c r="G6">
-        <v>-19.85350165586353</v>
+        <v>-27.25977633850085</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.72781362646861</v>
       </c>
       <c r="E7">
-        <v>-31.76287499886075</v>
+        <v>-37.50904887448266</v>
       </c>
       <c r="F7">
-        <v>-3.800840204229921</v>
+        <v>-5.153856389349839</v>
       </c>
       <c r="G7">
-        <v>-20.30838219986878</v>
+        <v>-25.19453554091853</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.30792932528495</v>
       </c>
       <c r="E8">
-        <v>-32.34574847381003</v>
+        <v>-38.1814049958235</v>
       </c>
       <c r="F8">
-        <v>-3.925070847354737</v>
+        <v>-5.140371925332829</v>
       </c>
       <c r="G8">
-        <v>-20.45205491045484</v>
+        <v>-24.98809488690789</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.84101194040319</v>
       </c>
       <c r="E9">
-        <v>-32.72479306943706</v>
+        <v>-38.60300592593761</v>
       </c>
       <c r="F9">
-        <v>-3.827477345874654</v>
+        <v>-4.644439960883671</v>
       </c>
       <c r="G9">
-        <v>-19.79848866536469</v>
+        <v>-24.80994615507586</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.314325012924858</v>
       </c>
       <c r="E10">
-        <v>-33.40698050784855</v>
+        <v>-38.29293225368441</v>
       </c>
       <c r="F10">
-        <v>-3.880537828865537</v>
+        <v>-5.071422120892342</v>
       </c>
       <c r="G10">
-        <v>-18.94934201090548</v>
+        <v>-26.1376934123292</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.733990712063159</v>
       </c>
       <c r="E11">
-        <v>-34.01464284951581</v>
+        <v>-40.51111920533558</v>
       </c>
       <c r="F11">
-        <v>-3.419764135739134</v>
+        <v>-4.881728993752836</v>
       </c>
       <c r="G11">
-        <v>-19.11276212563329</v>
+        <v>-25.23072973529939</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.104086625503449</v>
       </c>
       <c r="E12">
-        <v>-33.93675309658389</v>
+        <v>-39.62244240912234</v>
       </c>
       <c r="F12">
-        <v>-3.581085171403543</v>
+        <v>-4.433372346856435</v>
       </c>
       <c r="G12">
-        <v>-19.13696717934367</v>
+        <v>-26.21408756119342</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.429710882975303</v>
       </c>
       <c r="E13">
-        <v>-34.05229711088959</v>
+        <v>-41.08690788269986</v>
       </c>
       <c r="F13">
-        <v>-3.51044951201607</v>
+        <v>-4.292427271500071</v>
       </c>
       <c r="G13">
-        <v>-18.39076359370087</v>
+        <v>-26.04254833353055</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.739322335084793</v>
       </c>
       <c r="E14">
-        <v>-34.27373948986467</v>
+        <v>-39.05332643820837</v>
       </c>
       <c r="F14">
-        <v>-3.261408589401386</v>
+        <v>-5.145072364489853</v>
       </c>
       <c r="G14">
-        <v>-18.38036185961648</v>
+        <v>-24.72942541119694</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.051189510542248</v>
       </c>
       <c r="E15">
-        <v>-35.00864062996245</v>
+        <v>-42.63812986131633</v>
       </c>
       <c r="F15">
-        <v>-3.133462572198949</v>
+        <v>-4.451862113419192</v>
       </c>
       <c r="G15">
-        <v>-17.62769277853548</v>
+        <v>-23.51972062096462</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.37845386525473</v>
       </c>
       <c r="E16">
-        <v>-36.60296915265793</v>
+        <v>-41.3443425730879</v>
       </c>
       <c r="F16">
-        <v>-2.965314972186039</v>
+        <v>-3.6936058929896</v>
       </c>
       <c r="G16">
-        <v>-18.25972558016544</v>
+        <v>-24.28988096940236</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.741347236833323</v>
       </c>
       <c r="E17">
-        <v>-36.48884255071663</v>
+        <v>-40.67285818299354</v>
       </c>
       <c r="F17">
-        <v>-2.810652628043095</v>
+        <v>-4.116414196058131</v>
       </c>
       <c r="G17">
-        <v>-17.80497580270899</v>
+        <v>-23.47841659954391</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.152812427672123</v>
       </c>
       <c r="E18">
-        <v>-37.4090601683933</v>
+        <v>-42.03803459971589</v>
       </c>
       <c r="F18">
-        <v>-2.635017266461988</v>
+        <v>-4.198526180361836</v>
       </c>
       <c r="G18">
-        <v>-16.83015421848797</v>
+        <v>-23.74815488426541</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.615532358356956</v>
       </c>
       <c r="E19">
-        <v>-38.36163373285477</v>
+        <v>-42.98084250997982</v>
       </c>
       <c r="F19">
-        <v>-2.657458379283764</v>
+        <v>-4.036735575893499</v>
       </c>
       <c r="G19">
-        <v>-16.25242595061144</v>
+        <v>-24.23194642246512</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.130806914084205</v>
       </c>
       <c r="E20">
-        <v>-39.37157400604541</v>
+        <v>-44.20082699306823</v>
       </c>
       <c r="F20">
-        <v>-2.618777946005071</v>
+        <v>-3.296946950143847</v>
       </c>
       <c r="G20">
-        <v>-16.55843126171566</v>
+        <v>-24.16078459082571</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.705784825909971</v>
       </c>
       <c r="E21">
-        <v>-38.64999790071521</v>
+        <v>-45.78854847218653</v>
       </c>
       <c r="F21">
-        <v>-2.17528010885724</v>
+        <v>-3.43713897333742</v>
       </c>
       <c r="G21">
-        <v>-17.19030681243251</v>
+        <v>-22.80973605879421</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.339523731729938</v>
       </c>
       <c r="E22">
-        <v>-39.68429457135611</v>
+        <v>-44.97841126492531</v>
       </c>
       <c r="F22">
-        <v>-2.326676851402547</v>
+        <v>-3.06708628987105</v>
       </c>
       <c r="G22">
-        <v>-16.37321120461175</v>
+        <v>-23.36632483812972</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.0267812922701</v>
       </c>
       <c r="E23">
-        <v>-39.96253533557239</v>
+        <v>-44.31110439210303</v>
       </c>
       <c r="F23">
-        <v>-1.88617063472898</v>
+        <v>-2.830144088597367</v>
       </c>
       <c r="G23">
-        <v>-16.16086288208628</v>
+        <v>-22.38426971190539</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.772204114023462</v>
       </c>
       <c r="E24">
-        <v>-39.8821934139653</v>
+        <v>-44.12332668890097</v>
       </c>
       <c r="F24">
-        <v>-2.155186840055102</v>
+        <v>-4.117386591490211</v>
       </c>
       <c r="G24">
-        <v>-17.17323432908649</v>
+        <v>-22.42040597173931</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.573119150340806</v>
       </c>
       <c r="E25">
-        <v>-39.78338890382895</v>
+        <v>-46.79562674980432</v>
       </c>
       <c r="F25">
-        <v>-1.762808654298782</v>
+        <v>-3.386272714892379</v>
       </c>
       <c r="G25">
-        <v>-15.53679856356935</v>
+        <v>-23.37790181588056</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.423214419376762</v>
       </c>
       <c r="E26">
-        <v>-40.79767424782995</v>
+        <v>-47.16010324454867</v>
       </c>
       <c r="F26">
-        <v>-1.760238299598023</v>
+        <v>-4.007705454610536</v>
       </c>
       <c r="G26">
-        <v>-16.01827768570987</v>
+        <v>-21.70390625594761</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.319598350522482</v>
       </c>
       <c r="E27">
-        <v>-39.87151300801821</v>
+        <v>-45.16181446223596</v>
       </c>
       <c r="F27">
-        <v>-1.920001760494597</v>
+        <v>-3.560234891173825</v>
       </c>
       <c r="G27">
-        <v>-16.91273577696509</v>
+        <v>-21.88188118413883</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.260578072179698</v>
       </c>
       <c r="E28">
-        <v>-40.58685114040286</v>
+        <v>-44.85563301339235</v>
       </c>
       <c r="F28">
-        <v>-1.845676858177108</v>
+        <v>-3.911925296403632</v>
       </c>
       <c r="G28">
-        <v>-16.09856834667381</v>
+        <v>-22.56467954634075</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.241654409277406</v>
       </c>
       <c r="E29">
-        <v>-40.94559911552751</v>
+        <v>-45.50042884192251</v>
       </c>
       <c r="F29">
-        <v>-2.033611279897519</v>
+        <v>-3.690049681356481</v>
       </c>
       <c r="G29">
-        <v>-16.12757203614337</v>
+        <v>-21.7802093648095</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.256871720200379</v>
       </c>
       <c r="E30">
-        <v>-39.44085286565176</v>
+        <v>-44.72315250629795</v>
       </c>
       <c r="F30">
-        <v>-2.11242915589711</v>
+        <v>-3.453535872532923</v>
       </c>
       <c r="G30">
-        <v>-15.89548127529445</v>
+        <v>-20.26814086356617</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.306771379242104</v>
       </c>
       <c r="E31">
-        <v>-39.69608671767207</v>
+        <v>-47.12060363001677</v>
       </c>
       <c r="F31">
-        <v>-1.985499877892384</v>
+        <v>-3.614463357277345</v>
       </c>
       <c r="G31">
-        <v>-16.02761342413061</v>
+        <v>-22.56380225177284</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.388368094685984</v>
       </c>
       <c r="E32">
-        <v>-39.69594633497784</v>
+        <v>-43.87625088280546</v>
       </c>
       <c r="F32">
-        <v>-2.394605165527576</v>
+        <v>-3.214607704041277</v>
       </c>
       <c r="G32">
-        <v>-16.06190405482639</v>
+        <v>-19.98117118931275</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.495786352024356</v>
       </c>
       <c r="E33">
-        <v>-39.26458427914019</v>
+        <v>-45.25879626158423</v>
       </c>
       <c r="F33">
-        <v>-1.89672365909651</v>
+        <v>-4.219389922091834</v>
       </c>
       <c r="G33">
-        <v>-15.77533330131045</v>
+        <v>-22.77906882019118</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.626365999570807</v>
       </c>
       <c r="E34">
-        <v>-39.70026876341816</v>
+        <v>-44.47926701014086</v>
       </c>
       <c r="F34">
-        <v>-1.781404529157872</v>
+        <v>-3.737398528963332</v>
       </c>
       <c r="G34">
-        <v>-15.81887359624295</v>
+        <v>-20.4157945051632</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.778197078148577</v>
       </c>
       <c r="E35">
-        <v>-38.86607856646521</v>
+        <v>-46.3246654530066</v>
       </c>
       <c r="F35">
-        <v>-1.895661784280208</v>
+        <v>-4.220139014989837</v>
       </c>
       <c r="G35">
-        <v>-16.26868072920926</v>
+        <v>-20.06503723945911</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.947968859446007</v>
       </c>
       <c r="E36">
-        <v>-39.26545374614967</v>
+        <v>-46.54219975891306</v>
       </c>
       <c r="F36">
-        <v>-2.016700468132457</v>
+        <v>-3.755765558317641</v>
       </c>
       <c r="G36">
-        <v>-16.0567462248762</v>
+        <v>-22.3497622404768</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.13182033899588</v>
       </c>
       <c r="E37">
-        <v>-39.04139843767216</v>
+        <v>-46.38534700470939</v>
       </c>
       <c r="F37">
-        <v>-2.135896510152091</v>
+        <v>-4.530022751463874</v>
       </c>
       <c r="G37">
-        <v>-16.52135646222137</v>
+        <v>-23.04600472811369</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.33184810768398</v>
       </c>
       <c r="E38">
-        <v>-37.60911909310416</v>
+        <v>-45.52045828245843</v>
       </c>
       <c r="F38">
-        <v>-2.302185631273233</v>
+        <v>-3.927787694852674</v>
       </c>
       <c r="G38">
-        <v>-17.07880432812431</v>
+        <v>-22.31444865120939</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.548440922770548</v>
       </c>
       <c r="E39">
-        <v>-38.20428963922127</v>
+        <v>-43.79393228229404</v>
       </c>
       <c r="F39">
-        <v>-2.150679613019761</v>
+        <v>-4.09121743494349</v>
       </c>
       <c r="G39">
-        <v>-16.380818838261</v>
+        <v>-22.58182320641586</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.777390401234718</v>
       </c>
       <c r="E40">
-        <v>-37.49812166670215</v>
+        <v>-44.80037204507675</v>
       </c>
       <c r="F40">
-        <v>-2.028266272432911</v>
+        <v>-3.381453497791696</v>
       </c>
       <c r="G40">
-        <v>-16.40735948184933</v>
+        <v>-23.60445568931504</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.019975890434548</v>
       </c>
       <c r="E41">
-        <v>-36.95568520040437</v>
+        <v>-42.60481161380489</v>
       </c>
       <c r="F41">
-        <v>-2.052669596883917</v>
+        <v>-4.088225814469224</v>
       </c>
       <c r="G41">
-        <v>-17.3325874386193</v>
+        <v>-22.63183230733209</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.275048788665735</v>
       </c>
       <c r="E42">
-        <v>-36.70523115269915</v>
+        <v>-40.47646279375488</v>
       </c>
       <c r="F42">
-        <v>-1.922537273665216</v>
+        <v>-4.331810078352262</v>
       </c>
       <c r="G42">
-        <v>-16.28344907285995</v>
+        <v>-22.89462341223944</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.536646426741001</v>
       </c>
       <c r="E43">
-        <v>-36.06017720115055</v>
+        <v>-40.99428021110997</v>
       </c>
       <c r="F43">
-        <v>-1.922964082409427</v>
+        <v>-3.578134727283079</v>
       </c>
       <c r="G43">
-        <v>-16.9780693931826</v>
+        <v>-21.13295467478998</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.799916886601449</v>
       </c>
       <c r="E44">
-        <v>-35.44146991137858</v>
+        <v>-41.63632499168047</v>
       </c>
       <c r="F44">
-        <v>-2.127478321358573</v>
+        <v>-3.072265008214538</v>
       </c>
       <c r="G44">
-        <v>-17.43797534531646</v>
+        <v>-22.48120579584079</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.064034219810973</v>
       </c>
       <c r="E45">
-        <v>-35.2871553668562</v>
+        <v>-41.87371439187356</v>
       </c>
       <c r="F45">
-        <v>-2.124905591098941</v>
+        <v>-3.730421512552863</v>
       </c>
       <c r="G45">
-        <v>-16.39047901014459</v>
+        <v>-23.25588669421241</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.325582220883798</v>
       </c>
       <c r="E46">
-        <v>-35.47878906567579</v>
+        <v>-41.87141392707766</v>
       </c>
       <c r="F46">
-        <v>-2.022134954981287</v>
+        <v>-4.014536770076784</v>
       </c>
       <c r="G46">
-        <v>-16.81037536416359</v>
+        <v>-22.76870846792603</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.577762015553149</v>
       </c>
       <c r="E47">
-        <v>-34.7461815976629</v>
+        <v>-42.78684494772822</v>
       </c>
       <c r="F47">
-        <v>-2.260205546719722</v>
+        <v>-3.949523266689122</v>
       </c>
       <c r="G47">
-        <v>-16.53401764363631</v>
+        <v>-23.57517887983849</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.823503126323497</v>
       </c>
       <c r="E48">
-        <v>-34.71173349588655</v>
+        <v>-40.08736272159382</v>
       </c>
       <c r="F48">
-        <v>-2.084882175203956</v>
+        <v>-3.764514741647486</v>
       </c>
       <c r="G48">
-        <v>-16.56752864085758</v>
+        <v>-24.20699484073563</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.062645352081933</v>
       </c>
       <c r="E49">
-        <v>-33.92500170653398</v>
+        <v>-42.300237773234</v>
       </c>
       <c r="F49">
-        <v>-1.985384267360557</v>
+        <v>-4.230123488933725</v>
       </c>
       <c r="G49">
-        <v>-16.49660847904254</v>
+        <v>-22.56611963365033</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.289329688490405</v>
       </c>
       <c r="E50">
-        <v>-34.02322204352334</v>
+        <v>-39.41990867336629</v>
       </c>
       <c r="F50">
-        <v>-2.237431063802745</v>
+        <v>-3.906237416608331</v>
       </c>
       <c r="G50">
-        <v>-16.7704981878703</v>
+        <v>-22.02969869774006</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.506219096900057</v>
       </c>
       <c r="E51">
-        <v>-33.14010394915451</v>
+        <v>-38.97918626175478</v>
       </c>
       <c r="F51">
-        <v>-2.149057898162351</v>
+        <v>-4.21066845361551</v>
       </c>
       <c r="G51">
-        <v>-16.68312792527062</v>
+        <v>-23.95810802709322</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.714846747393397</v>
       </c>
       <c r="E52">
-        <v>-32.23427782187422</v>
+        <v>-39.08364230745271</v>
       </c>
       <c r="F52">
-        <v>-1.812652630575407</v>
+        <v>-3.596763859966393</v>
       </c>
       <c r="G52">
-        <v>-17.43440988777067</v>
+        <v>-23.95190075420709</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.91153088330018</v>
       </c>
       <c r="E53">
-        <v>-33.16739253352473</v>
+        <v>-39.73197487418287</v>
       </c>
       <c r="F53">
-        <v>-1.892270278062295</v>
+        <v>-3.681968030069994</v>
       </c>
       <c r="G53">
-        <v>-17.38870449605549</v>
+        <v>-22.65089277327445</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.093520671420386</v>
       </c>
       <c r="E54">
-        <v>-32.16266000544291</v>
+        <v>-38.66175381923912</v>
       </c>
       <c r="F54">
-        <v>-1.922200736158185</v>
+        <v>-3.440694393117582</v>
       </c>
       <c r="G54">
-        <v>-17.79142905036229</v>
+        <v>-22.03636117063784</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.263078689499262</v>
       </c>
       <c r="E55">
-        <v>-31.49140203904893</v>
+        <v>-39.3519091076671</v>
       </c>
       <c r="F55">
-        <v>-1.850946639610733</v>
+        <v>-3.515987731602362</v>
       </c>
       <c r="G55">
-        <v>-17.84741203070413</v>
+        <v>-23.39537818578237</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.417604517033761</v>
       </c>
       <c r="E56">
-        <v>-31.31319300142508</v>
+        <v>-38.35757169166989</v>
       </c>
       <c r="F56">
-        <v>-2.10696299492997</v>
+        <v>-3.806558174437614</v>
       </c>
       <c r="G56">
-        <v>-17.29989911196454</v>
+        <v>-23.17944454243786</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.548550526360424</v>
       </c>
       <c r="E57">
-        <v>-30.95410991922386</v>
+        <v>-38.60090018552404</v>
       </c>
       <c r="F57">
-        <v>-1.788410844127776</v>
+        <v>-3.189631078048882</v>
       </c>
       <c r="G57">
-        <v>-17.77125127530043</v>
+        <v>-24.646310854888</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.659839672442948</v>
       </c>
       <c r="E58">
-        <v>-30.39725932015967</v>
+        <v>-35.46681804463652</v>
       </c>
       <c r="F58">
-        <v>-2.139683150995907</v>
+        <v>-3.847950704096498</v>
       </c>
       <c r="G58">
-        <v>-17.40328413861044</v>
+        <v>-23.03901947702583</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.749818215159083</v>
       </c>
       <c r="E59">
-        <v>-29.88130989833275</v>
+        <v>-37.64995913594233</v>
       </c>
       <c r="F59">
-        <v>-1.969547208206162</v>
+        <v>-3.761147782871262</v>
       </c>
       <c r="G59">
-        <v>-18.32842933174193</v>
+        <v>-23.3305212881225</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.811502267722232</v>
       </c>
       <c r="E60">
-        <v>-30.13756492124179</v>
+        <v>-35.68239604977166</v>
       </c>
       <c r="F60">
-        <v>-1.877192605894353</v>
+        <v>-3.492738136910753</v>
       </c>
       <c r="G60">
-        <v>-16.91531965775848</v>
+        <v>-24.5437104275349</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.848159165279486</v>
       </c>
       <c r="E61">
-        <v>-30.76617145519453</v>
+        <v>-34.87019838683696</v>
       </c>
       <c r="F61">
-        <v>-2.052986338067005</v>
+        <v>-4.461586859592948</v>
       </c>
       <c r="G61">
-        <v>-18.41069638839282</v>
+        <v>-24.80854579431275</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.862306505953016</v>
       </c>
       <c r="E62">
-        <v>-29.87203105509103</v>
+        <v>-35.31456395578763</v>
       </c>
       <c r="F62">
-        <v>-1.906282116149145</v>
+        <v>-4.184724183308781</v>
       </c>
       <c r="G62">
-        <v>-17.88201550795337</v>
+        <v>-25.55651224545522</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.851649383294462</v>
       </c>
       <c r="E63">
-        <v>-29.52676434708722</v>
+        <v>-34.58937186396229</v>
       </c>
       <c r="F63">
-        <v>-1.98844953015989</v>
+        <v>-3.725447884125426</v>
       </c>
       <c r="G63">
-        <v>-18.42166091521889</v>
+        <v>-24.88225012492632</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.815756562332241</v>
       </c>
       <c r="E64">
-        <v>-28.9903281088496</v>
+        <v>-35.247476877601</v>
       </c>
       <c r="F64">
-        <v>-2.547231655716221</v>
+        <v>-4.055072514835415</v>
       </c>
       <c r="G64">
-        <v>-18.16308082423749</v>
+        <v>-25.80458963071327</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.760010150607197</v>
       </c>
       <c r="E65">
-        <v>-27.90528762271575</v>
+        <v>-36.43398688082471</v>
       </c>
       <c r="F65">
-        <v>-2.365589297597852</v>
+        <v>-4.291510305775032</v>
       </c>
       <c r="G65">
-        <v>-18.37976761669218</v>
+        <v>-24.05769585800558</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.683841482085723</v>
       </c>
       <c r="E66">
-        <v>-28.25836368414579</v>
+        <v>-37.5300315587972</v>
       </c>
       <c r="F66">
-        <v>-2.377126595191828</v>
+        <v>-4.319438959593807</v>
       </c>
       <c r="G66">
-        <v>-18.3858176386652</v>
+        <v>-24.18276495793371</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.580963030940759</v>
       </c>
       <c r="E67">
-        <v>-29.48341552964879</v>
+        <v>-35.13911049459744</v>
       </c>
       <c r="F67">
-        <v>-2.283135232816412</v>
+        <v>-4.559436921431331</v>
       </c>
       <c r="G67">
-        <v>-18.41123269677018</v>
+        <v>-25.57770966854317</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.456138870407172</v>
       </c>
       <c r="E68">
-        <v>-28.60913022383192</v>
+        <v>-38.00119663692526</v>
       </c>
       <c r="F68">
-        <v>-2.499113127034467</v>
+        <v>-4.642468247018948</v>
       </c>
       <c r="G68">
-        <v>-17.93387189328051</v>
+        <v>-24.11987452432417</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.307077203287054</v>
       </c>
       <c r="E69">
-        <v>-29.12308032438445</v>
+        <v>-35.34124346040382</v>
       </c>
       <c r="F69">
-        <v>-2.581560065139286</v>
+        <v>-4.379912769974862</v>
       </c>
       <c r="G69">
-        <v>-18.27461972454662</v>
+        <v>-23.13361997108327</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.12725977803703</v>
       </c>
       <c r="E70">
-        <v>-28.64164013873299</v>
+        <v>-36.00487094809488</v>
       </c>
       <c r="F70">
-        <v>-2.573216310523794</v>
+        <v>-4.210303409402001</v>
       </c>
       <c r="G70">
-        <v>-18.51507126815496</v>
+        <v>-23.26911894473287</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.920069989006774</v>
       </c>
       <c r="E71">
-        <v>-28.72074805117298</v>
+        <v>-37.41783635102016</v>
       </c>
       <c r="F71">
-        <v>-3.029309360817116</v>
+        <v>-4.717707739502603</v>
       </c>
       <c r="G71">
-        <v>-17.77154922439897</v>
+        <v>-22.52363209219932</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.688826198644468</v>
       </c>
       <c r="E72">
-        <v>-28.60583802322834</v>
+        <v>-35.89846313009964</v>
       </c>
       <c r="F72">
-        <v>-2.907702918394182</v>
+        <v>-4.724278535345761</v>
       </c>
       <c r="G72">
-        <v>-17.63178295754925</v>
+        <v>-24.42869710968231</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.433688965712197</v>
       </c>
       <c r="E73">
-        <v>-28.798692145793</v>
+        <v>-34.81140294455837</v>
       </c>
       <c r="F73">
-        <v>-3.068456987340864</v>
+        <v>-4.251935870507073</v>
       </c>
       <c r="G73">
-        <v>-18.03714436137808</v>
+        <v>-23.35739298626477</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.157846406372343</v>
       </c>
       <c r="E74">
-        <v>-28.51829809218607</v>
+        <v>-33.86060680614491</v>
       </c>
       <c r="F74">
-        <v>-2.904704963096255</v>
+        <v>-4.918336355988219</v>
       </c>
       <c r="G74">
-        <v>-18.03679509882368</v>
+        <v>-23.56107099002289</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.870452450237362</v>
       </c>
       <c r="E75">
-        <v>-29.27072216245653</v>
+        <v>-37.22434371362042</v>
       </c>
       <c r="F75">
-        <v>-2.946610613471741</v>
+        <v>-5.296011416025599</v>
       </c>
       <c r="G75">
-        <v>-17.60250780334547</v>
+        <v>-23.72322813162747</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.575967874260655</v>
       </c>
       <c r="E76">
-        <v>-28.51190388688724</v>
+        <v>-34.85306264119193</v>
       </c>
       <c r="F76">
-        <v>-2.85460046719654</v>
+        <v>-4.682279446321266</v>
       </c>
       <c r="G76">
-        <v>-16.75290429360184</v>
+        <v>-23.39056961838658</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.274974293411325</v>
       </c>
       <c r="E77">
-        <v>-29.96792828491446</v>
+        <v>-36.00149497072216</v>
       </c>
       <c r="F77">
-        <v>-3.501592636683975</v>
+        <v>-5.747717600933154</v>
       </c>
       <c r="G77">
-        <v>-17.16818409186633</v>
+        <v>-22.63850140132095</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.978781002403463</v>
       </c>
       <c r="E78">
-        <v>-28.97445127897871</v>
+        <v>-35.96923865036552</v>
       </c>
       <c r="F78">
-        <v>-3.488736112062438</v>
+        <v>-5.051884732866523</v>
       </c>
       <c r="G78">
-        <v>-16.78076087904204</v>
+        <v>-23.50282028598664</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.6924715428952</v>
       </c>
       <c r="E79">
-        <v>-29.45259699978959</v>
+        <v>-40.02960656409999</v>
       </c>
       <c r="F79">
-        <v>-3.390688878837582</v>
+        <v>-5.780450426646413</v>
       </c>
       <c r="G79">
-        <v>-17.26600243618794</v>
+        <v>-20.52168892532787</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.417669507121503</v>
       </c>
       <c r="E80">
-        <v>-30.24167227444113</v>
+        <v>-35.84088358309211</v>
       </c>
       <c r="F80">
-        <v>-3.25343067085236</v>
+        <v>-4.677723124402546</v>
       </c>
       <c r="G80">
-        <v>-16.95035019538228</v>
+        <v>-20.85549785314366</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.161676747066161</v>
       </c>
       <c r="E81">
-        <v>-30.3793310915633</v>
+        <v>-38.64402257926209</v>
       </c>
       <c r="F81">
-        <v>-3.140479181257303</v>
+        <v>-4.88115806777032</v>
       </c>
       <c r="G81">
-        <v>-16.84440280648899</v>
+        <v>-21.90236849520861</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.930037828415059</v>
       </c>
       <c r="E82">
-        <v>-31.92351355733484</v>
+        <v>-37.8163103643771</v>
       </c>
       <c r="F82">
-        <v>-3.502050327693537</v>
+        <v>-5.208724672643196</v>
       </c>
       <c r="G82">
-        <v>-16.24320277073903</v>
+        <v>-20.70751977808377</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.723559465014437</v>
       </c>
       <c r="E83">
-        <v>-31.02461373104928</v>
+        <v>-39.7332926601191</v>
       </c>
       <c r="F83">
-        <v>-3.763945399370885</v>
+        <v>-5.048911325010286</v>
       </c>
       <c r="G83">
-        <v>-16.20757136909986</v>
+        <v>-22.07476018834785</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.542277763193949</v>
       </c>
       <c r="E84">
-        <v>-32.92429046337097</v>
+        <v>-37.73561748603442</v>
       </c>
       <c r="F84">
-        <v>-3.460782118949016</v>
+        <v>-4.946436050045861</v>
       </c>
       <c r="G84">
-        <v>-16.62707376819968</v>
+        <v>-19.68103050963135</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.390351700908266</v>
       </c>
       <c r="E85">
-        <v>-32.95830609587959</v>
+        <v>-40.06229761796137</v>
       </c>
       <c r="F85">
-        <v>-3.669531187516047</v>
+        <v>-5.24500183219521</v>
       </c>
       <c r="G85">
-        <v>-16.41599338461575</v>
+        <v>-21.23877129713447</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.26640361586077</v>
       </c>
       <c r="E86">
-        <v>-33.59709490363856</v>
+        <v>-41.77737337159737</v>
       </c>
       <c r="F86">
-        <v>-3.566911795313318</v>
+        <v>-4.340939351101812</v>
       </c>
       <c r="G86">
-        <v>-16.13301126246439</v>
+        <v>-19.76848684641504</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.165209472761039</v>
       </c>
       <c r="E87">
-        <v>-34.5447414883797</v>
+        <v>-41.15581993591158</v>
       </c>
       <c r="F87">
-        <v>-3.648767219258721</v>
+        <v>-5.698222831810882</v>
       </c>
       <c r="G87">
-        <v>-15.78587407830749</v>
+        <v>-19.4098388954181</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.088143807319909</v>
       </c>
       <c r="E88">
-        <v>-34.98731151738632</v>
+        <v>-41.18774794190266</v>
       </c>
       <c r="F88">
-        <v>-3.396052890773175</v>
+        <v>-5.315989866148867</v>
       </c>
       <c r="G88">
-        <v>-16.1287423139915</v>
+        <v>-19.1397679008699</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.032601959622736</v>
       </c>
       <c r="E89">
-        <v>-36.29914024606131</v>
+        <v>-42.76328103322931</v>
       </c>
       <c r="F89">
-        <v>-3.634229590807944</v>
+        <v>-5.623707092930583</v>
       </c>
       <c r="G89">
-        <v>-15.63455566279848</v>
+        <v>-18.9744061511833</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.993377518570512</v>
       </c>
       <c r="E90">
-        <v>-37.67439704592473</v>
+        <v>-43.22512651184959</v>
       </c>
       <c r="F90">
-        <v>-3.775705999498939</v>
+        <v>-5.422722142613994</v>
       </c>
       <c r="G90">
-        <v>-15.18473859819555</v>
+        <v>-21.25731862851824</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.967464571954653</v>
       </c>
       <c r="E91">
-        <v>-38.2216699224627</v>
+        <v>-44.64171242974401</v>
       </c>
       <c r="F91">
-        <v>-3.621799874930618</v>
+        <v>-5.51097653031073</v>
       </c>
       <c r="G91">
-        <v>-15.60210404014978</v>
+        <v>-20.14852919795953</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.951865402271988</v>
       </c>
       <c r="E92">
-        <v>-39.31777120636028</v>
+        <v>-44.45688955583196</v>
       </c>
       <c r="F92">
-        <v>-4.074168840763784</v>
+        <v>-5.86208254805774</v>
       </c>
       <c r="G92">
-        <v>-16.15633074524301</v>
+        <v>-20.209602142068</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.940531945080588</v>
       </c>
       <c r="E93">
-        <v>-40.75721459680842</v>
+        <v>-46.58120576977814</v>
       </c>
       <c r="F93">
-        <v>-3.899272277992229</v>
+        <v>-5.361750256722533</v>
       </c>
       <c r="G93">
-        <v>-15.91675484092981</v>
+        <v>-20.31734715718912</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.926118000062645</v>
       </c>
       <c r="E94">
-        <v>-42.29990266615744</v>
+        <v>-47.00820237667239</v>
       </c>
       <c r="F94">
-        <v>-4.096680428498798</v>
+        <v>-6.020984472936314</v>
       </c>
       <c r="G94">
-        <v>-15.69183968753726</v>
+        <v>-20.45640496729344</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.904820384920295</v>
       </c>
       <c r="E95">
-        <v>-42.91803936820444</v>
+        <v>-47.15619517148006</v>
       </c>
       <c r="F95">
-        <v>-4.074161714087165</v>
+        <v>-5.355846992922732</v>
       </c>
       <c r="G95">
-        <v>-15.94118170119132</v>
+        <v>-23.14420378517232</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.869537508016474</v>
       </c>
       <c r="E96">
-        <v>-44.80123698361221</v>
+        <v>-50.67054006750267</v>
       </c>
       <c r="F96">
-        <v>-4.071470997736832</v>
+        <v>-5.830787727315699</v>
       </c>
       <c r="G96">
-        <v>-15.40594925112965</v>
+        <v>-18.87677154213911</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.81437633171484</v>
       </c>
       <c r="E97">
-        <v>-45.5410424610603</v>
+        <v>-50.98929482442858</v>
       </c>
       <c r="F97">
-        <v>-4.131957477765211</v>
+        <v>-6.326567655996976</v>
       </c>
       <c r="G97">
-        <v>-15.47158743753678</v>
+        <v>-20.40424566704945</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.73480383582776</v>
       </c>
       <c r="E98">
-        <v>-48.07960762756914</v>
+        <v>-52.0874814706067</v>
       </c>
       <c r="F98">
-        <v>-4.599242577762944</v>
+        <v>-5.9197001448203</v>
       </c>
       <c r="G98">
-        <v>-15.39838134402688</v>
+        <v>-20.86797695455394</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.630937536034305</v>
       </c>
       <c r="E99">
-        <v>-49.88750124870336</v>
+        <v>-55.68494424280311</v>
       </c>
       <c r="F99">
-        <v>-4.535299659574119</v>
+        <v>-5.202522880278335</v>
       </c>
       <c r="G99">
-        <v>-16.07676012793386</v>
+        <v>-21.40435650864497</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.496406916485006</v>
       </c>
       <c r="E100">
-        <v>-51.70446313903794</v>
+        <v>-56.14899622038362</v>
       </c>
       <c r="F100">
-        <v>-4.609368793386264</v>
+        <v>-5.755037489674314</v>
       </c>
       <c r="G100">
-        <v>-16.35857362750986</v>
+        <v>-22.26157923894723</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.339147294521084</v>
       </c>
       <c r="E101">
-        <v>-52.09646256668241</v>
+        <v>-56.23646935643428</v>
       </c>
       <c r="F101">
-        <v>-4.409473432739497</v>
+        <v>-5.981682435085812</v>
       </c>
       <c r="G101">
-        <v>-16.23495289125517</v>
+        <v>-20.06050013679754</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.150894635105534</v>
       </c>
       <c r="E102">
-        <v>-54.25226412828542</v>
+        <v>-56.35565313172366</v>
       </c>
       <c r="F102">
-        <v>-4.545010152394636</v>
+        <v>-6.387226759970138</v>
       </c>
       <c r="G102">
-        <v>-16.44220793946847</v>
+        <v>-20.57491587650827</v>
       </c>
     </row>
   </sheetData>
